--- a/resources/templates/standard/H1100-04.xlsx
+++ b/resources/templates/standard/H1100-04.xlsx
@@ -35,7 +35,7 @@
 </t>
   </si>
   <si>
-    <t>삼보 네고   예상가</t>
+    <t>고객사 네고   예상가</t>
   </si>
   <si>
     <t>년간 매출금액</t>
@@ -97,7 +97,7 @@
     <t>{{companyName}} 사내공정 Flow</t>
   </si>
   <si>
-    <t>삼보 제출가      원</t>
+    <t>고객사 제출가      원</t>
   </si>
 </sst>
 </file>
